--- a/Plots/Comparison Table of k and p Values.xlsx
+++ b/Plots/Comparison Table of k and p Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olincollege-my.sharepoint.com/personal/kyue_olin_edu/Documents/Documents/MATLAB/Numerical Methods/Assignment-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olincollege-my.sharepoint.com/personal/mepstein_olin_edu/Documents/Desktop/Applied Math/Assignment-1/Plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2EE308-B5DF-418E-A7BB-A41033188973}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54E985CD-A3E6-4B31-B6C0-858FC20D056F}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,18 +47,6 @@
     <t>Method</t>
   </si>
   <si>
-    <t>Predicted k value</t>
-  </si>
-  <si>
-    <t>Measured k value</t>
-  </si>
-  <si>
-    <t>Predicted p value</t>
-  </si>
-  <si>
-    <t>Measured p value</t>
-  </si>
-  <si>
     <t>Bisection Method</t>
   </si>
   <si>
@@ -72,6 +60,18 @@
   </si>
   <si>
     <t>Fzero Method</t>
+  </si>
+  <si>
+    <t>Predicted k value (-)</t>
+  </si>
+  <si>
+    <t>Measured k value (-)</t>
+  </si>
+  <si>
+    <t>Predicted p value (-)</t>
+  </si>
+  <si>
+    <t>Measured p value (-)</t>
   </si>
 </sst>
 </file>
@@ -523,10 +523,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
@@ -543,27 +543,27 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>0.5</v>
       </c>
       <c r="C3" s="2">
-        <v>0.49730000000000002</v>
+        <v>0.50339999999999996</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>3.73E-2</v>
@@ -591,10 +591,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2">
         <v>0.1522</v>
@@ -608,16 +608,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>0.12429999999999999</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E6" s="3">
         <v>1.6648000000000001</v>

--- a/Plots/Comparison Table of k and p Values.xlsx
+++ b/Plots/Comparison Table of k and p Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olincollege-my.sharepoint.com/personal/mepstein_olin_edu/Documents/Desktop/Applied Math/Assignment-1/Plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54E985CD-A3E6-4B31-B6C0-858FC20D056F}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{F5548F79-425C-4B76-B71C-57BD59B12E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2F6BD4C-BBEF-4D68-A110-3A497DD32E91}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="8880" xr2:uid="{D244108E-BDF8-4038-A556-2A9E06F46F59}"/>
   </bookViews>
@@ -525,7 +525,7 @@
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
